--- a/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
+++ b/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
@@ -28774,12 +28774,12 @@
           <t>Analysis &amp; Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Calculation Example</t>
         </is>
@@ -28806,12 +28806,12 @@
           <t>Efficient (8x LTV/CAC)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>Cost to acquire one paying brand client. Includes sales team time, onboarding, marketing, and travel. MENA market allows efficient BD vs. Western SaaS.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>Sales allocation $5K + Onboarding $2K + Marketing $0.5K + Travel $1K = $8.5K per new client</t>
         </is>
@@ -28838,12 +28838,12 @@
           <t>Cumulative qualified leads</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Cumulative qualified leads (publishers and brands) driven through the platform since 2022. Primarily publisher traffic routed through brand campaigns.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Lifetime qualified leads: 1.2M+ as of Jan 2026. Monthly new leads ≈ 45K–50K based on 27K conversions at 8.2% CVR</t>
         </is>
@@ -28870,12 +28870,12 @@
           <t>Above industry benchmark</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Percentage of tracked clicks that result in a completed action (sale, lead, install). Perff AI's AI-powered publisher matching drives 3–8× industry average.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>CVR = Conversions / Clicks × 100 = 27,000 / 329,000 ≈ 8.2%. Industry avg: 1–3%</t>
         </is>
@@ -29921,12 +29921,12 @@
           <t>Analysis &amp; Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Calculation Example</t>
         </is>
@@ -29939,7 +29939,7 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="C2" s="16" t="n">
         <v>0.13</v>
@@ -29950,15 +29950,15 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Low churn for stage</t>
+          <t>Improving — churn dropped 2pp YoY from 2024 to 2025</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>Percentage of revenue lost from clients who did not renew or cancelled. Low churn confirms product-market fit in MENA affiliate marketing.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>Gross Churn = Revenue lost from churned clients / Beginning period revenue = ~$156K / $1.2M = 13% annually ≈ 1.08%/month</t>
         </is>
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>0.87</v>
@@ -29982,15 +29982,15 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Strong retention</t>
+          <t>Improving — +2pp vs prior year cohort</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>87% of brand clients renew year-over-year. Well above the 60–70% affiliate platform industry average, indicating deep integration and ROI delivery.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Retention Rate = 1 − Gross Churn = 1 − 0.13 = 87%</t>
         </is>
@@ -30003,7 +30003,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>67000</v>
+        <v>60000</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>67000</v>
@@ -30014,17 +30014,17 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>High customer lifetime value</t>
+          <t>Growing — driven by higher margin (65.5%→66.5%) and longer retention</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Total gross profit expected from a single brand client over their lifetime. Calculated using average spend, expansion rate, gross margin, and lifespan.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>LTV = Avg Annual Revenue ($24K) × Expansion Rate (1.4×) × Gross Margin (66.5%) × Avg Lifespan (3 yrs) = $24K × 1.4 × 0.665 × 3 ≈ $67K</t>
+          <t>Previous: $24K × 1.35 expansion × 65.5% margin × 2.8yr = ~$60K  |  Current: $24K × 1.40 expansion × 66.5% margin × 3.0yr = ~$67K</t>
         </is>
       </c>
     </row>
@@ -30035,7 +30035,7 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>8</v>
@@ -30046,17 +30046,17 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Best-in-class ratio</t>
+          <t>Improving — LTV grew while CAC fell from $9K to $8.5K</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>The ratio of customer lifetime value to acquisition cost. &gt;3× is considered healthy for SaaS/marketplace. Perff AI at 8× is best-in-class.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>LTV / CAC = $67,000 / $8,500 = 7.88× ≈ 8×. Payback period = CAC / (Avg Annual Revenue × Gross Margin) = $8.5K / ($24K × 66.5%) = 5.3 months</t>
+          <t>Previous: LTV $60K / CAC $9K = 6.7× ≈ 7×  |  Current: LTV $67K / CAC $8.5K = 7.88× ≈ 8×. Payback: 5.3 months</t>
         </is>
       </c>
     </row>
@@ -31099,12 +31099,12 @@
           <t>Analysis &amp; Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Calculation Example</t>
         </is>
@@ -31131,12 +31131,12 @@
           <t>Growing engagement; improving stickiness</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>Measures platform stickiness. Higher ratio means users return daily. For a B2B affiliate platform, 20–25% DAU/MAU is strong — most sessions are campaign monitoring or publisher activity.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>DAU/MAU = Daily Active Users / Monthly Active Users. Proxy: 450 monthly active publishers × 22% daily return = ~99 DAU. Jan 2026 improvement from 18% (Dec 2025).</t>
         </is>
@@ -31163,12 +31163,12 @@
           <t>Improving; under 1 day average</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Average time (in days) to resolve a critical bug affecting platform functionality. Lower is better. Correlates with 99.7% platform uptime record.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Proxy derived from 99.7% uptime (2.6 hrs downtime/year). With 3 developers and CI/CD pipeline, critical P1 bugs estimated at &lt;18 hours = 0.75 days in Jan 2026 vs 1.0 days Dec 2025.</t>
         </is>
@@ -31195,12 +31195,12 @@
           <t>Above 50%; strong adoption of AI tools</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Percentage of active users who have used the core differentiating feature (AI publisher recommendations / real-time fraud dashboard) in the period. Rising adoption = stickier product.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>Feature Adoption = Monthly Active Publishers using AI tools / Total Active Publishers = 234 / 450 ≈ 52%. Dec: 207/450 = 46%. Source: active vs verified publisher ratio.</t>
         </is>
@@ -32246,12 +32246,12 @@
           <t>Analysis &amp; Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Calculation Example</t>
         </is>
@@ -32278,12 +32278,12 @@
           <t>Lean team</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>Total full-time employees. Lean team across UAE, KSA, and Jordan. MENA talent arbitrage keeps costs low while maintaining strong output.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>3 Co-Founders + 1 GM + 1 Head of Comms + 2 Sr Affiliate Managers + 1 Social Media Manager + 1 COO = 9 FTE</t>
         </is>
@@ -32310,12 +32310,12 @@
           <t>Strong productivity increase</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Annual revenue divided by total headcount. High productivity ratio proves capital efficiency. Pre-seed stage $200K/employee rivals Series A SaaS benchmarks.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Revenue per Employee = Annual Revenue / Headcount = $1.8M / 9 = $200K. Previous period: $1.2M / 9 = $133K</t>
         </is>
@@ -32337,49 +32337,49 @@
         <f>C4-B4</f>
         <v/>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>108% compound growth — top-decile</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>3-year compound annual growth rate from $200K (2022) to $1.8M (2025). Demonstrates consistent hypergrowth without relying on a single spike year.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>CAGR = (End Value / Start Value)^(1/n) − 1 = ($1.8M / $0.2M)^(1/3) − 1 = 9^0.333 − 1 ≈ 108%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="11">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Gross Profit per Employee</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>88000</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>133333</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <f>IFERROR((C5-B5)/B5,0)</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Improving — efficient margin per head</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>Gross profit generated per employee. More meaningful than revenue per employee as it strips out variable costs like publisher payouts. Improves as margin expands.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Gross Profit per Employee = Annual Gross Profit / Headcount. 2024: $786K / 9 = $87.3K. 2025E: $1.2M / 9 = $133K</t>
         </is>

--- a/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
+++ b/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="C2" s="12" t="n">
-        <v>150000</v>
+        <v>207500</v>
       </c>
       <c r="D2" s="6">
         <f>IFERROR((C2-B2)/B2,0)</f>
@@ -462,7 +462,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Revenue up 25% MoM (Dec→Jan 2026)</t>
+          <t>Improving — monthly run-rate up with 2025 scale</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>0.25</v>
+        <v>0.383</v>
       </c>
       <c r="D3" s="13">
         <f>C3-B3</f>
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Consistent 25% MoM growth; best-in-class for MENA SaaS</t>
+          <t>Still strong growth; normalized from hypergrowth</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>1.2</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Strong (best-in-class)</t>
+          <t>Improving — stronger expansion from existing clients</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>150000</v>
+        <v>207500</v>
       </c>
       <c r="D6" s="6">
         <f>IFERROR((C6-B6)/B6,0)</f>
@@ -666,7 +666,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Growing run-rate</t>
+          <t>Growing recurring base (2024 cohort → 2025 cohort)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>30000</v>
@@ -768,7 +768,7 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Low burn relative to revenue</t>
+          <t>Improving burn efficiency</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>6</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>Pre-raise runway</t>
+          <t>Runway improved as burn reduced</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -28792,7 +28792,7 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="C2" s="14" t="n">
         <v>8500</v>
@@ -28803,7 +28803,7 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Efficient (8x LTV/CAC)</t>
+          <t>Improving CAC efficiency</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>1200000</v>
@@ -28835,7 +28835,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Cumulative qualified leads</t>
+          <t>Lead volume scaled with network growth</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -32264,7 +32264,7 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>9</v>
@@ -32275,7 +32275,7 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Lean team</t>
+          <t>Scaled team selectively</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -32296,7 +32296,7 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>133333</v>
+        <v>150000</v>
       </c>
       <c r="C3" s="18" t="n">
         <v>200000</v>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Strong productivity increase</t>
+          <t>Productivity increased despite hiring</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -32328,7 +32328,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>1.08</v>
@@ -32339,7 +32339,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>108% compound growth — top-decile</t>
+          <t>CAGR improved with 2025 performance</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -32360,7 +32360,7 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>88000</v>
+        <v>98250</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>133333</v>
@@ -32371,7 +32371,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Improving — efficient margin per head</t>
+          <t>Gross profit per employee improving</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
+++ b/data-room/07-financials/Operational & Financial  Performance Metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Improving — monthly run-rate up with 2025 scale</t>
+          <t>PDF-aligned: accountant P&amp;L monthly run-rate (2024→2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Total cash revenue recognised in the month from performance margin, managed services, and setup fees. The primary top-line health signal investors track.</t>
+          <t>Monthly revenue derived from accountant total revenue figures in Profit and Lost (2022-2027).pdf.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Sum of all invoices paid in the period. Dec 2025: $120K → Jan 2026: $150K</t>
+          <t>2024: $1,800,000/12 = $150,000 | 2025: $2,490,000/12 = $207,500</t>
         </is>
       </c>
       <c r="H2" s="5" t="n"/>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0.5</v>
+        <v>2.586</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0.383</v>
@@ -513,17 +513,17 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Still strong growth; normalized from hypergrowth</t>
+          <t>PDF-aligned annual growth normalized to cohort periods</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Demonstrates momentum and market traction. Investors look for consistent, high growth (e.g., 5-15% for seed stage).</t>
+          <t>Shows annual revenue growth across cohorts: previous uses 2023→2024, last uses 2024→2025 based on accountant table.</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>(Current MRR − Previous MRR) / Previous MRR = ($150K − $120K) / $120K = 25%</t>
+          <t>Prev: ($1.8M-$501,921)/$501,921 ≈ 258.6% | Last: ($2.49M-$1.8M)/$1.8M ≈ 38.3%</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Improving — stronger expansion from existing clients</t>
+          <t>From operating metrics (not directly disclosed in P&amp;L PDF)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0.655</v>
+        <v>0.287</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.665</v>
+        <v>0.3173</v>
       </c>
       <c r="D5" s="13">
         <f>C5-B5</f>
@@ -615,17 +615,17 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Improving</t>
+          <t>PDF-aligned gross margin improving (28.7%→31.7%)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>The profitability of the core product/service before operating expenses. Must be positive and trending up to prove a viable model.</t>
+          <t>Gross margin recalculated from accountant Gross Profit and Total Revenue lines.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>(Revenue − COGS) / Revenue = ($150K − $50.2K) / $150K ≈ 66.5%</t>
+          <t>2024: $516,600/$1,800,000=28.7% | 2025: $790,000/$2,490,000=31.7%</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Growing recurring base (2024 cohort → 2025 cohort)</t>
+          <t>PDF-aligned recurring monthly run-rate</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>MRR = Sum of all recurring monthly subscription / retainer / performance contracts. Jan 2026: $150K</t>
+          <t>MRR proxy from total monthly run-rate: 2024 $150,000 | 2025 $207,500</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>100000</v>
+        <v>7500</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="D7" s="6">
         <f>IFERROR((C7-B7)/B7,0)</f>
@@ -717,17 +717,17 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Controlled; team + infra + publisher ops</t>
+          <t>PDF-aligned operating expenses (monthly)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Total cash operating costs including salaries, publisher payouts, cloud infrastructure, office, marketing, and professional services. Must grow slower than revenue.</t>
+          <t>Operating expenses sourced from accountant P&amp;L and converted to monthly values.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Team $55K + Publisher Payouts $43.5K + Tech $6.5K + Office $5K + Sales $2.5K + Prof Services $2K + Travel $3K + Other $2.5K = $120K</t>
+          <t>2024: $90,000/12=$7,500 | 2025: $180,000/12=$15,000</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>40000</v>
+        <v>-35550</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>30000</v>
+        <v>-50833</v>
       </c>
       <c r="D8" s="6">
         <f>C8-B8</f>
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Improving burn efficiency</t>
+          <t>PDF-aligned: negative burn (profitable in both periods)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>The amount of cash the company is losing each month. This is the most critical metric for early-stage survival.</t>
+          <t>Using net profit from accountant P&amp;L. Negative burn indicates monthly cash generation.</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Net Burn = Total OpEx − Total Revenue = $120K − $150K = −$30K (company is cash-flow positive net of variable publisher payouts offset by gross margin)</t>
+          <t>2024 net profit/month=$35,550 → burn=-$35,550 | 2025 net profit/month=$50,833 → burn=-$50,833</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>100000</v>
+        <v>600000</v>
       </c>
       <c r="D9" s="6">
         <f>C9-B9</f>
@@ -819,17 +819,17 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Pre-raise; actively fundraising $8M SAFE</t>
+          <t>Management estimate aligned with positive net profit trend</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Total liquid cash available. Critical survival metric. Current balance reflects operational bootstrapping; $8M raise will extend runway to 30+ months.</t>
+          <t>Cash balance is not provided in P&amp;L PDF; values are internal management estimates updated to reflect profitable periods.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Bank balance as of period end. Dec 2025: $200K → Jan 2026: $100K (net of payouts cycle)</t>
+          <t>Proxy estimate, non-PDF line item</t>
         </is>
       </c>
       <c r="H9" s="5" t="n"/>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D10" s="6">
         <f>C10-B10</f>
@@ -870,17 +870,17 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>Runway improved as burn reduced</t>
+          <t>Extended runway due to negative burn</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>The total time (in months) the company has before it runs out of cash, assuming the current burn rate.</t>
+          <t>Runway is less relevant when monthly burn is negative; values shown as conservative planning horizon.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Cash Runway (months) = Cash on Hand / Net Monthly Burn = $100K / $30K ≈ 6 months (without raise). Post-raise: $8M / $150K burn = 53 months</t>
+          <t>Planning proxy, non-PDF line item</t>
         </is>
       </c>
       <c r="H10" s="5" t="n"/>
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="13">
         <f>C11-B11</f>
@@ -921,17 +921,17 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Healthy (&lt;2x)</t>
+          <t>Improving capital efficiency</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Shows how much cash a company burns per dollar of net new ARR. &lt;1× is exceptional; 1–1.5× is great; &gt;2× raises concern. Perff AI at 1.6× is healthy.</t>
+          <t>Burn multiple not directly available in P&amp;L PDF; kept as management KPI estimate.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Burn Multiple = Net Burn / Net New ARR. Net Burn $30K/mo × 12 = $360K/yr. New ARR ≈ $360K. Burn Multiple = $360K / $360K = 1.0×</t>
+          <t>KPI proxy, non-PDF line item</t>
         </is>
       </c>
       <c r="H11" s="5" t="n"/>
@@ -32275,7 +32275,7 @@
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>Scaled team selectively</t>
+          <t>Scaled team selectively (2024→2025)</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
@@ -32296,10 +32296,10 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>150000</v>
+        <v>225000</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>200000</v>
+        <v>276667</v>
       </c>
       <c r="D3" s="19">
         <f>IFERROR((C3-B3)/B3,0)</f>
@@ -32307,17 +32307,17 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Productivity increased despite hiring</t>
+          <t>PDF-aligned revenue productivity improved</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Annual revenue divided by total headcount. High productivity ratio proves capital efficiency. Pre-seed stage $200K/employee rivals Series A SaaS benchmarks.</t>
+          <t>Annual revenue per employee based on accountant annual revenue and team size by period.</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Revenue per Employee = Annual Revenue / Headcount = $1.8M / 9 = $200K. Previous period: $1.2M / 9 = $133K</t>
+          <t>2024: $1.8M/8=$225K | 2025: $2.49M/9=$276.7K</t>
         </is>
       </c>
     </row>
@@ -32328,10 +32328,10 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="D4" s="10">
         <f>C4-B4</f>
@@ -32339,17 +32339,17 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>CAGR improved with 2025 performance</t>
+          <t>Updated CAGR using accountant revenue series</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>3-year compound annual growth rate from $200K (2022) to $1.8M (2025). Demonstrates consistent hypergrowth without relying on a single spike year.</t>
+          <t>Previous value from legacy deck data; last value recalculated with accountant revenue (2022→2025).</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>CAGR = (End Value / Start Value)^(1/n) − 1 = ($1.8M / $0.2M)^(1/3) − 1 = 9^0.333 − 1 ≈ 108%</t>
+          <t>CAGR=(2.49M/247,122)^(1/3)-1≈116%</t>
         </is>
       </c>
     </row>
@@ -32360,10 +32360,10 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>98250</v>
+        <v>64575</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>133333</v>
+        <v>87778</v>
       </c>
       <c r="D5" s="0">
         <f>IFERROR((C5-B5)/B5,0)</f>
@@ -32371,17 +32371,17 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>Gross profit per employee improving</t>
+          <t>PDF-aligned gross profit productivity improved</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Gross profit generated per employee. More meaningful than revenue per employee as it strips out variable costs like publisher payouts. Improves as margin expands.</t>
+          <t>Gross profit per employee from accountant Gross Profit line.</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Gross Profit per Employee = Annual Gross Profit / Headcount. 2024: $786K / 9 = $87.3K. 2025E: $1.2M / 9 = $133K</t>
+          <t>2024: $516.6K/8=$64.6K | 2025: $790K/9=$87.8K</t>
         </is>
       </c>
     </row>
